--- a/daily_matches/job_matches_2026-09-14.xlsx
+++ b/daily_matches/job_matches_2026-09-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Cloud Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,85 +478,85 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Redshift, Apache Airflow, CI/CD, Git, Snowflake, Databricks</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27110d8079f69f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=70a18d3647cd00e8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Applied AI/ML Senior Associate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, Prompt Engineering, Azure ML, MLflow, Git, Snowflake, Databricks</t>
+          <t>RAG, TensorFlow, PyTorch, spaCy, MLflow, FastAPI, Apache Airflow, CI/CD, Databricks, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1028ad7a9aa73a</t>
+          <t>https://www.indeed.com/viewjob?jk=eae6c6ee7ee4ee8e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Engineer II (Middleware)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Generative AI, LangChain, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e66b988bfbe6b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f5a03e9857d6b23e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Applied AI/ML Senior Associate</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks, PySpark</t>
+          <t>RAG, TensorFlow, PyTorch, S3, EC2, Kubernetes, CI/CD, Dask, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5186558c260f0015</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d0e797b63177f5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI and Machine Learning Engineering Graduate</t>
+          <t>1158 Senior AI Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Intetics Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Tableau, Matplotlib, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8659a53ca35cc3f</t>
+          <t>https://www.indeed.com/viewjob?jk=2462fc392cb118f7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Expert Data Scientist</t>
+          <t>Marketing Data Scientist Senior Associate - Consumer Bank</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, TensorFlow, Git, Hadoop, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Copilot, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,84 +671,84 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd46d25f4490d62a</t>
+          <t>https://www.indeed.com/viewjob?jk=bda6f7d9817a58e1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applied AI/ML Senior Associate - Payments</t>
+          <t>Solution Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks, PySpark, Python</t>
+          <t>RAG, Prompt Engineering, S3, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4339ab2034b2a1e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c3199068b458165b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Azure Cloud &amp; Platform Engineer</t>
+          <t>Software Engineer III - GenAI Patterns</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Farmers and Merchants Bank of Long Beach</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seal Beach, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e0da53c55c9779</t>
+          <t>https://www.indeed.com/viewjob?jk=ad94727708755e48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III - Agentic AI, Java/Python</t>
+          <t>Data for Good Hackathon - Data &amp; AI Program - 2027 Summer Internship - United States</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, Polars, Dask, Python, R</t>
+          <t>RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,357 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb9e314fca7d4987</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Engineer II (Middleware)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ross Dress For Less</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=572e256f7e9350b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Internal Audit, Asset Wealth Management - Senior Associate - Data Scientist</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Git, Snowflake, Databricks, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d278006464037da3</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Quant Analytics Senior Associate - Credit Card Installment</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29e210016aa20709</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Quant Analyst- Senior Associate</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d24442a00077965</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Associate Data Scientist</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Databricks, Hadoop, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=def7b99a8f909fd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2027 Data &amp; AI Program - Summer Internship - Analyst - United States</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fcf80d98b8560ed5</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Scientist — Global Services Insights &amp; Analytics, Commercial Banking - Sr. Associate</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Kubernetes, Databricks, Hadoop, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a260dcc256f6e1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer II Data Reliability &amp; Automation (APIs)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Sony Interactive Entertainment</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Kubernetes, Terraform, Kafka, Cassandra, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e2f2c758029e494</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AI Data Scientist - Senior Associate</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Snowflake, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca71be4a7c36f4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Scientist Senior Associate</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=52dd0b528e3d2393</t>
+          <t>https://www.indeed.com/viewjob?jk=4428ba5b6407ce18</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-14.xlsx
+++ b/daily_matches/job_matches_2026-09-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer III</t>
+          <t>Sr Data Analyst- Supply Chain Management</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sierra Space</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Louisville, CO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, TensorFlow, PyTorch, CI/CD, Jenkins, Git, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70a18d3647cd00e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fc30bf38932d48</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Applied AI/ML Senior Associate</t>
+          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, spaCy, MLflow, FastAPI, Apache Airflow, CI/CD, Databricks, Python</t>
+          <t>Data Scientist, RAG, S3, Glue, CI/CD, Jenkins, Git, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eae6c6ee7ee4ee8e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b7312f22356e37b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer II (Middleware)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,77 +556,77 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5a03e9857d6b23e</t>
+          <t>https://www.indeed.com/viewjob?jk=4ffdb43d383ec427</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Core specialty</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, S3, EC2, Kubernetes, CI/CD, Dask, Python, R</t>
+          <t>Synapse, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d0e797b63177f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b44d832238c13ae8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1158 Senior AI Developer</t>
+          <t>Infrastructure Engineer (Automation &amp; AI)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intetics Inc</t>
+          <t>Marmon Foodservice Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McAllen, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, Python, R</t>
+          <t>AI Engineer, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,54 +636,54 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2462fc392cb118f7</t>
+          <t>https://www.indeed.com/viewjob?jk=bc6a6b745282fca9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marketing Data Scientist Senior Associate - Consumer Bank</t>
+          <t>Senior Infrastructure Engineer, Core Systems</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>QuickNode</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hallandale Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Git, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda6f7d9817a58e1</t>
+          <t>https://www.indeed.com/viewjob?jk=44dbc0a1e62ab6b6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Solution Engineer - Remote</t>
+          <t>Senior Software Engineer - Integrations - AI/ML</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Kafka, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3199068b458165b</t>
+          <t>https://www.indeed.com/viewjob?jk=e5a3f6a634403376</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - GenAI Patterns</t>
+          <t>AI Enablement Partner</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Copilot, Cortex, CI/CD, Git, Snowflake, Databricks, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad94727708755e48</t>
+          <t>https://www.indeed.com/viewjob?jk=0cdcbe8d2012cead</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data for Good Hackathon - Data &amp; AI Program - 2027 Summer Internship - United States</t>
+          <t>Data Scientist Senior Associate - Consumer Bank Marketing Analytics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,25 +758,130 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db20ac89b89cf409</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IT Solutions Engineer – AI, Automation &amp; Cloud</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dev Technology Group</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, Snowflake, Databricks, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4428ba5b6407ce18</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, CI/CD, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e5f5c455eeaa834</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Oteemo, Inc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, PyTorch, Python, R, Scala, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b391743d7b75ac93</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Focus</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, MLflow, CI/CD, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6193bc1e7abc47f6</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-14.xlsx
+++ b/daily_matches/job_matches_2026-09-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Analyst- Supply Chain Management</t>
+          <t>Sr. AI Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sierra Space</t>
+          <t>Park Place Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Louisville, CO, US USA</t>
+          <t>Highland Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, TensorFlow, PyTorch, CI/CD, Jenkins, Git, Kafka</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, PyTorch, Azure ML, Glue, Synapse, Data Lake, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fc30bf38932d48</t>
+          <t>https://www.indeed.com/viewjob?jk=1e8be741f2af4076</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Java/React Developer - Data Scientist Senior Associate</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, CI/CD, Jenkins, Git, Kafka, PostgreSQL, Python</t>
+          <t>Data Scientist, RAG, Glue, Redshift, BigQuery, Synapse, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7312f22356e37b</t>
+          <t>https://www.indeed.com/viewjob?jk=dca7148f734ca29b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>AI Engineer-3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ffdb43d383ec427</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d81efdf722a4ba</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Hyperscale Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Core specialty</t>
+          <t>Veeam Software</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Synapse, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Synapse, Data Lake, Docker, Kubernetes, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b44d832238c13ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=f17632f11610e0ed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Automation &amp; AI)</t>
+          <t>Senior Data Engineer - Life Sciences.AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marmon Foodservice Technologies</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McAllen, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, BigQuery, CI/CD, Terraform, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc6a6b745282fca9</t>
+          <t>https://www.indeed.com/viewjob?jk=6a2b7a80aec3b5d1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer, Core Systems</t>
+          <t>Senior AI/ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>QuickNode</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hallandale Beach, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44dbc0a1e62ab6b6</t>
+          <t>https://www.indeed.com/viewjob?jk=99a928f03071d76d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations - AI/ML</t>
+          <t>Senior Data Scientist - Life Sciences.AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Kafka, Tableau, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, Git, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5a3f6a634403376</t>
+          <t>https://www.indeed.com/viewjob?jk=07475910816a72ec</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Enablement Partner</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Cortex, CI/CD, Git, Snowflake, Databricks, R, Scala</t>
+          <t>Data Scientist, RAG, S3, Athena, Data Lake, Kubernetes, Apache Airflow, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cdcbe8d2012cead</t>
+          <t>https://www.indeed.com/viewjob?jk=30987ecce424f169</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate - Consumer Bank Marketing Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, CI/CD, Terraform, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db20ac89b89cf409</t>
+          <t>https://www.indeed.com/viewjob?jk=2d6a3b442efcc911</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT Solutions Engineer – AI, Automation &amp; Cloud</t>
+          <t>Agentic AI Engineer -3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dev Technology Group</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Git, Python, R, Java, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, Pinecone, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e5f5c455eeaa834</t>
+          <t>https://www.indeed.com/viewjob?jk=5ff2184ceecaa288</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Oteemo, Inc</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, PyTorch, Python, R, Scala, Optimization, Bayesian</t>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Power BI, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,882 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b391743d7b75ac93</t>
+          <t>https://www.indeed.com/viewjob?jk=866494264fa824bd</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer (AI-Enabled Engineering)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Focus</t>
+          <t>DENSO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Southfield, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e37af820dfbced57</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior ML Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Symbotic</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=573ecddae507313b</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gen AI Engineer-2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1db2986f8833e5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Snowflake, Databricks, PySpark, Kafka, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76a3f3303ca4a1e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer, AI Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Vivint</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, OpenCV, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa34c35a22c8ed33</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Solutions Architect – Data Analytics (Hybrid - Newport News, VA)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ferguson</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Newport News, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74a88f1cd0bc4605</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>The University of Southern MIssissippi</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Gulfport, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, Keras, Docker, MongoDB, NoSQL, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98d9e47ce2e3b125</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bbe5902aba9bae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nextPoint</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28cb7e036c4cfede</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Applied AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Databricks, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e2b9168d8c2689f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Prompt Engineer IV</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tango</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ed68b0175131219</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist – Healthcare Analytics</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Watson, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Hadoop, PostgreSQL, Dask, Python, SQL, R, Bayesian, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4782d437ac23c24f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Analyst/Sr Analyst, Sales AI &amp; Innovation</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, MLflow, Databricks, PySpark, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14a7057bfbd5c605</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sr Data Engineering Architect – Fraud Domain-5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Lake, Snowflake, Databricks, PySpark, Kafka, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9cc5633ac50e4a9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SDMyers</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tallmadge, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Azure ML, FastAPI, CI/CD, Git, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41ba530e6e53139a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gallup</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28fa3b790be3d6fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Thundr Inc.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, MLflow, CI/CD, Git, Snowflake, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6193bc1e7abc47f6</t>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, OpenCV, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ad9fccf8d836fe7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Southern Company</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fd1100a529927b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Junior Data Scientist - Generative AI and Japanese Language</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>App Orchid Inc</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, TensorFlow, PyTorch, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ea98880693c6ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior .NET Developer-6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bee32a137e976deb</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ensemble Health Partners</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Blue Ash, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Dataflow, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95e649e74f85aa42</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI Prototyping &amp; Transformation Associate</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9379d26b50677a4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Blink Health</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Git, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ef0de51766f7f65</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02ff6f6e6edf5293</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Python, Pyspark, GKP, Postgress</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Databricks, PySpark, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=89b8853567513f32</t>
         </is>
       </c>
     </row>
